--- a/artfynd/A 12045-2026 artfynd.xlsx
+++ b/artfynd/A 12045-2026 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132614896</v>
+        <v>133030111</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tannsjön S, Jmt</t>
+          <t>Skiftessundet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533016</v>
+        <v>533072</v>
       </c>
       <c r="R2" t="n">
-        <v>7040740</v>
+        <v>7040607</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132614897</v>
+        <v>133030089</v>
       </c>
       <c r="B3" t="n">
-        <v>80438</v>
+        <v>83358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tannsjön S, Jmt</t>
+          <t>Skiftessundet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533193</v>
+        <v>533092</v>
       </c>
       <c r="R3" t="n">
-        <v>7040668</v>
+        <v>7040704</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,9 +850,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132614900</v>
+        <v>132614896</v>
       </c>
       <c r="B4" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533022</v>
+        <v>533016</v>
       </c>
       <c r="R4" t="n">
-        <v>7040701</v>
+        <v>7040740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132614899</v>
+        <v>132614897</v>
       </c>
       <c r="B5" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533085</v>
+        <v>533193</v>
       </c>
       <c r="R5" t="n">
-        <v>7040760</v>
+        <v>7040668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1086,7 @@
         <v>132614898</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133030111</v>
+        <v>132614899</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skiftessundet, Jmt</t>
+          <t>Tannsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533072</v>
+        <v>533085</v>
       </c>
       <c r="R7" t="n">
-        <v>7040607</v>
+        <v>7040760</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1228,19 +1248,9 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,48 +1277,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133030119</v>
+        <v>132614900</v>
       </c>
       <c r="B8" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skiftessundet, Jmt</t>
+          <t>Tannsjön S, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532985</v>
+        <v>533022</v>
       </c>
       <c r="R8" t="n">
-        <v>7040777</v>
+        <v>7040701</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1335,19 +1345,9 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133030104</v>
+        <v>133030102</v>
       </c>
       <c r="B9" t="n">
-        <v>80439</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533060</v>
+        <v>532915</v>
       </c>
       <c r="R9" t="n">
-        <v>7040611</v>
+        <v>7040728</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133030106</v>
+        <v>133030103</v>
       </c>
       <c r="B10" t="n">
-        <v>80439</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533092</v>
+        <v>532928</v>
       </c>
       <c r="R10" t="n">
-        <v>7040654</v>
+        <v>7040633</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133030098</v>
+        <v>133030104</v>
       </c>
       <c r="B11" t="n">
-        <v>80468</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133030108</v>
+        <v>133030106</v>
       </c>
       <c r="B12" t="n">
-        <v>80439</v>
+        <v>80488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532978</v>
+        <v>533092</v>
       </c>
       <c r="R12" t="n">
-        <v>7040784</v>
+        <v>7040654</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133030089</v>
+        <v>133030107</v>
       </c>
       <c r="B13" t="n">
-        <v>83319</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533092</v>
+        <v>533108</v>
       </c>
       <c r="R13" t="n">
-        <v>7040704</v>
+        <v>7040659</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133030103</v>
+        <v>133030108</v>
       </c>
       <c r="B14" t="n">
-        <v>80439</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532928</v>
+        <v>532978</v>
       </c>
       <c r="R14" t="n">
-        <v>7040633</v>
+        <v>7040784</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,32 +2016,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133030107</v>
+        <v>133030098</v>
       </c>
       <c r="B15" t="n">
-        <v>80439</v>
+        <v>80493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533108</v>
+        <v>533060</v>
       </c>
       <c r="R15" t="n">
-        <v>7040659</v>
+        <v>7040611</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,32 +2123,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133030102</v>
+        <v>133030119</v>
       </c>
       <c r="B16" t="n">
-        <v>80439</v>
+        <v>80499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532915</v>
+        <v>532985</v>
       </c>
       <c r="R16" t="n">
-        <v>7040728</v>
+        <v>7040777</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,7 +2233,7 @@
         <v>133030110</v>
       </c>
       <c r="B17" t="n">
-        <v>80475</v>
+        <v>80500</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12045-2026 artfynd.xlsx
+++ b/artfynd/A 12045-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030111</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614896</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614898</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614899</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614900</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030102</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030103</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030104</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030107</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030108</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030098</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030119</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2334,6 +2414,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030110</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2436,8 +2521,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614881</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>